--- a/data/trans_dic/P37A$medicootras-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicootras-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,85</t>
+          <t>0,48; 3,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,01</t>
+          <t>0,62; 2,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,85</t>
+          <t>0,14; 1,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,13</t>
+          <t>0,13; 1,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,9</t>
+          <t>0,73; 2,41</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,54</t>
+          <t>0,26; 2,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,9</t>
+          <t>0,17; 1,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,43</t>
+          <t>0,26; 2,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,97</t>
+          <t>0,99; 3,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,15</t>
+          <t>0,12; 1,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,73</t>
+          <t>0,26; 1,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,52</t>
+          <t>0,26; 1,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,89</t>
+          <t>0,66; 1,93</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,19</t>
+          <t>0,19; 1,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,22</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 5,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,37</t>
+          <t>0,14; 1,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,06</t>
+          <t>0,28; 1,69</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,35</t>
+          <t>0,0; 0,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,1</t>
+          <t>0,24; 1,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,54</t>
+          <t>0,43; 1,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,19</t>
+          <t>0,26; 1,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,09</t>
+          <t>0,12; 1,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,09</t>
+          <t>0,55; 2,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,96</t>
+          <t>0,71; 2,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,43</t>
+          <t>0,04; 0,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,9</t>
+          <t>0,24; 0,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,53</t>
+          <t>0,61; 1,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,29</t>
+          <t>0,56; 1,41</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -1282,64 +1282,64 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,26</t>
+          <t>0,15; 1,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,59</t>
+          <t>0,25; 1,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,03</t>
+          <t>0,82; 2,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,9</t>
+          <t>0,15; 0,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,09</t>
+          <t>0,18; 1,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,4</t>
+          <t>0,58; 1,61</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1442,37 +1442,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,63</t>
+          <t>0,49; 1,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,92</t>
+          <t>0,09; 0,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,84</t>
+          <t>0,52; 1,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,35</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,6</t>
+          <t>0,48; 1,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,8</t>
+          <t>0,14; 0,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,42</t>
+          <t>0,42; 1,35</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,48</t>
+          <t>0,11; 0,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,87</t>
+          <t>0,28; 0,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,87</t>
+          <t>0,34; 0,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,02</t>
+          <t>0,42; 1,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,08</t>
+          <t>0,49; 1,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,99</t>
+          <t>0,4; 0,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,57</t>
+          <t>0,98; 1,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,35</t>
+          <t>0,13; 0,36</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,84</t>
+          <t>0,44; 0,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,81</t>
+          <t>0,43; 0,81</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,16</t>
+          <t>0,79; 1,26</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>13969</t>
         </is>
       </c>
     </row>
@@ -1927,22 +1927,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 9919</t>
+          <t>0; 9532</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 9976</t>
+          <t>0; 9983</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6710</t>
+          <t>0; 6541</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3018; 19461</t>
+          <t>2644; 19244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1952,37 +1952,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 9883</t>
+          <t>0; 11519</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6451</t>
+          <t>0; 6271</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3090; 13457</t>
+          <t>3040; 13006</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 10162</t>
+          <t>0; 9621</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1050; 13894</t>
+          <t>1038; 14513</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1001; 8793</t>
+          <t>988; 8953</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7974; 27644</t>
+          <t>7619; 25019</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>10893</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6006</t>
+          <t>0; 5998</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 11899</t>
+          <t>0; 11608</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>980; 9575</t>
+          <t>980; 9623</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>727; 8575</t>
+          <t>815; 8551</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6175</t>
+          <t>0; 6205</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>881; 8199</t>
+          <t>891; 7865</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7780</t>
+          <t>0; 6874</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3080; 11361</t>
+          <t>4174; 13559</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>887; 8528</t>
+          <t>886; 9371</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1886; 13113</t>
+          <t>1973; 14270</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2038; 11377</t>
+          <t>1967; 12174</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5404; 15819</t>
+          <t>5958; 17526</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4994</t>
         </is>
       </c>
     </row>
@@ -2343,32 +2343,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6842</t>
+          <t>0; 6316</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 7409</t>
+          <t>0; 6755</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5501</t>
+          <t>0; 4944</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>153; 7938</t>
+          <t>877; 9053</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7074</t>
+          <t>0; 7071</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 12836</t>
+          <t>0; 13244</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3954</t>
+          <t>0; 3938</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1020; 9739</t>
+          <t>1024; 9975</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1071; 13293</t>
+          <t>1064; 13276</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4535</t>
+          <t>0; 5937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>711; 8826</t>
+          <t>1814; 11119</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>18134</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4275</t>
+          <t>0; 4212</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2774; 12794</t>
+          <t>2784; 13806</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5249; 17673</t>
+          <t>4964; 18053</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2799; 12293</t>
+          <t>2912; 13367</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6211</t>
+          <t>0; 7074</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>944; 8320</t>
+          <t>940; 7801</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4709; 17269</t>
+          <t>4504; 16795</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5053; 19175</t>
+          <t>6123; 18496</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>848; 8339</t>
+          <t>849; 7709</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4753; 17385</t>
+          <t>4603; 16507</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11928; 30206</t>
+          <t>12135; 30769</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9624; 25905</t>
+          <t>11191; 28063</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>13635</t>
         </is>
       </c>
     </row>
@@ -2764,64 +2764,64 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5478</t>
+          <t>0; 5868</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7614</t>
+          <t>0; 9850</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 6670</t>
+          <t>0; 8251</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6932</t>
+          <t>0; 6873</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>982; 9604</t>
+          <t>1124; 8921</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1829; 11746</t>
+          <t>1821; 12575</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4827; 17080</t>
+          <t>6838; 18957</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5948</t>
+          <t>0; 7447</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1932; 11444</t>
+          <t>1923; 11918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2316; 14772</t>
+          <t>2429; 15436</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6237; 18441</t>
+          <t>8046; 22540</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8560</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5740</t>
+          <t>0; 4731</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 8306</t>
+          <t>0; 8203</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5305</t>
+          <t>0; 6366</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2992,37 +2992,37 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5230; 18106</t>
+          <t>5394; 19277</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1019; 9988</t>
+          <t>1015; 9247</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4343; 13999</t>
+          <t>4368; 14374</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5441</t>
+          <t>0; 4787</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6968; 22042</t>
+          <t>6630; 22526</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1820; 11021</t>
+          <t>1888; 11072</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4290; 14177</t>
+          <t>4581; 14585</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>47142</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>62956</t>
+          <t>70185</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2915; 15645</t>
+          <t>3522; 16015</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10319; 29940</t>
+          <t>9453; 28560</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11834; 29317</t>
+          <t>11444; 30065</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12169; 34572</t>
+          <t>14500; 35971</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2966; 14137</t>
+          <t>2988; 14305</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16505; 38370</t>
+          <t>17294; 38982</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14503; 34878</t>
+          <t>14177; 35004</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31338; 56329</t>
+          <t>35449; 59421</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8321; 23236</t>
+          <t>8393; 23853</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30191; 58607</t>
+          <t>30381; 58139</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30318; 56059</t>
+          <t>29794; 56209</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>48861; 80759</t>
+          <t>56153; 88964</t>
         </is>
       </c>
     </row>
